--- a/DataDrivenFrameWork/src/test/resources/dataset.xlsx
+++ b/DataDrivenFrameWork/src/test/resources/dataset.xlsx
@@ -12,12 +12,11 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>password</t>
   </si>
@@ -35,6 +34,9 @@
   </si>
   <si>
     <t>abc</t>
+  </si>
+  <si>
+    <t>UserName</t>
   </si>
 </sst>
 </file>
@@ -384,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -403,28 +405,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1"/>
-    <hyperlink ref="A3" r:id="rId2"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
